--- a/www/download/COUNTRY.FRA.rpO1.xlsx
+++ b/www/download/COUNTRY.FRA.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>França</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>0.760282826729216</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.779672363475178</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.88864406087171</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.89809338282399</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.938262381425976</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>1.08271976661779</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>1.11656987383435</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>1.05752963960776</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.884017005403936</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>0.803923182788067</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.803793923948273</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>0.796431999963391</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>0.729660724914413</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902077640803</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948697621517</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22.694</t>
+          <t>2.13887912756863</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>2.05139475990129</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.879</t>
+          <t>2.10658105493921</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.227</t>
+          <t>2.10811717104517</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>23.696</t>
+          <t>2.23344292476534</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>24.332</t>
+          <t>2.18613324935992</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>24.765</t>
+          <t>2.11204866416857</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.919</t>
+          <t>2.217148384835</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>2.5967572194878</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24.977</t>
+          <t>2.29781463430861</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>25.115</t>
+          <t>2.38071959428739</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>25.362</t>
+          <t>2.35496714392183</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>25.729</t>
+          <t>2.26007190170275</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>25.945</t>
+          <t>2.19868826421731</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>25.522</t>
+          <t>2.14719934995446</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20.264</t>
+          <t>3.92912572579614</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20.419</t>
+          <t>3.79787212167379</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20.574</t>
+          <t>3.61536225030962</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.968</t>
+          <t>3.64282267607651</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>21.455</t>
+          <t>3.79170759713889</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>22.102</t>
+          <t>3.74256104461494</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22.56</t>
+          <t>3.63108040984055</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22.725</t>
+          <t>3.67427422747505</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22.759</t>
+          <t>3.96397219196689</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22.768</t>
+          <t>3.60266109971136</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>22.875</t>
+          <t>3.62191115723243</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>23.097</t>
+          <t>3.51311084857638</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>23.444</t>
+          <t>3.44114833058475</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>3.3502806938248</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>23.244</t>
+          <t>3.29214993185368</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>35398.487</t>
+          <t>4.56427659086556</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>35593.522</t>
+          <t>4.48170934400427</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35567.12</t>
+          <t>4.25394504904076</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35886.025</t>
+          <t>4.20060202720066</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>36560.307</t>
+          <t>4.40512082702045</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>36624.674</t>
+          <t>4.29798848120359</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>37045.329</t>
+          <t>4.17788443964869</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36392.365</t>
+          <t>4.17318876859861</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>36304.468</t>
+          <t>3.4176727513367</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>36998.921</t>
+          <t>4.10708634845003</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>37190.257</t>
+          <t>4.11019172777077</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>37129.413</t>
+          <t>3.9876463828031</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>38094.743</t>
+          <t>3.96350147479619</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>38629.06</t>
+          <t>3.82204301430594</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>37490.919</t>
+          <t>3.74648778744976</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>31468.573</t>
+          <t>57304285035683.1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>31797.298</t>
+          <t>51313112643083.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31910.139</t>
+          <t>47689601054992.2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>32356.773</t>
+          <t>53934098922407.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>33060.697</t>
+          <t>58923652556603</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>33182.202</t>
+          <t>62507892615338.7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>33644.776</t>
+          <t>66997050651384.3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>33067.66</t>
+          <t>69304364647223</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>33001.137</t>
+          <t>79962110333458.3</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>33623.177</t>
+          <t>76102096339213.8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>33760.725</t>
+          <t>71094670784256.7</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>33683.49</t>
+          <t>64271929715988.4</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>34563.816</t>
+          <t>54919695188620.4</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>34927.705</t>
+          <t>43012919555341.5</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>34397.205</t>
+          <t>39043579173997</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>14612837107906.7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>13140067769145.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>12142305587366.9</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29.46</t>
+          <t>13839342053202.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>14756674890282.2</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>15271069086000.3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>16534057978593.4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>17494173237977.5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>20441878364881.5</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>19223220762475.3</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>32.68</t>
+          <t>17723808792035</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>15968154268439</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>13568254950049.9</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>11286524680308.3</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>37.49</t>
+          <t>10392051204485.5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>880163912.270545</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>808658357.363415</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>831834192.110751</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>908217588.088886</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>980459298.533565</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>1108563699.16116</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>1175114268.38386</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>1136702032.36965</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>1084607971.15956</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>900473546.331524</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>805626741.170855</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>684116893.904034</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>43.83</t>
+          <t>506770613.010677</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>358759119.395302</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>42.37</t>
+          <t>353935418.683947</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>1592479.72738204</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>1607993.80873384</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>1472999.82725092</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>1515572.59761256</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>1520425.92235709</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>1394167.43940641</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>1422693.96617389</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>1574666.47406632</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>1942162.4269654</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>2223502.06835081</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>2302536.24887913</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2407689.80863973</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>2749198.01023791</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>3050111.33827569</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>2923757.87399039</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>2576210.54916012</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>2591093.33732387</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>2357533.33760878</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>2419628.92931087</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>2464098.90802912</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>2304836.11507252</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>2335946.03224799</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>2526404.14479532</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>3062760.01368446</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>3503478.1956295</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>3663683.6504919</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>3841945.61810293</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>4378021.53379428</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>4568309.38538071</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>28.83</t>
+          <t>4317218.3514631</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>43.94</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>47.93</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>46.62</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>368936.495761504</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>374764.48329163</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>335780.252283257</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>341390.915017351</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>336675.801301864</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>304371.927123232</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>304156.833678665</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>325909.107965684</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>391806.062005809</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>446675.660307622</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>467880.918878405</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>27.41</t>
+          <t>495782.294355566</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>568435.887594481</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.760282826729216</t>
+          <t>721133.707462442</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.779672363475178</t>
+          <t>643512.156104531</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.88864406087171</t>
+          <t>590168.588353769</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89809338282399</t>
+          <t>660034.627387117</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262381425976</t>
+          <t>687783.722991985</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976661779</t>
+          <t>690929.820832331</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987383435</t>
+          <t>732895.889547089</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752963960776</t>
+          <t>769827.37968992</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017005403936</t>
+          <t>898180.883549576</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923182788067</t>
+          <t>844293.879344849</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793923948273</t>
+          <t>774818.0876788</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431999963391</t>
+          <t>691357.862060503</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660724914413</t>
+          <t>578751.704062871</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902077640803</t>
+          <t>478646.175389769</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948697621517</t>
+          <t>447077.654874891</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>734732507791.871</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>403329027027.692</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>635104146560.945</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>985734888206.567</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>1025843197505.66</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>1167972916232.52</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1303901750931.17</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1293728145867.78</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>1175163235111.87</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>962857908700.921</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>980288645613.024</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.176</t>
+          <t>783943822089.248</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>497558236125.719</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>643619674619.245</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.408</t>
+          <t>620391799443.869</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>779574823809.434</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>489075790867.07</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>605299971013.581</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>1037896362348.73</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>1160149531750.18</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>1291710325114.73</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>1491391090934.79</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1401968120669.64</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>1399025204656.22</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.164</t>
+          <t>1285976826212.66</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.208</t>
+          <t>1121474240641.87</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>1035543632367.99</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>768587879162.404</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.607</t>
+          <t>869377933412.519</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.522</t>
+          <t>835801415531.073</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.606</t>
+          <t>-44842316017.5631</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6.597</t>
+          <t>-85746763839.3782</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5.931</t>
+          <t>29804175547.3637</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5.983</t>
+          <t>-52161474142.1585</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5.843</t>
+          <t>-134306334244.517</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5.252</t>
+          <t>-123737408882.207</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5.273</t>
+          <t>-187489340003.612</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5.791</t>
+          <t>-108239974801.859</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7.146</t>
+          <t>-223861969544.351</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8.308</t>
+          <t>-323118917511.738</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>8.753</t>
+          <t>-141185595028.847</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9.475</t>
+          <t>-251599810278.743</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>10.893</t>
+          <t>-271029643036.685</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-225758258793.274</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-215409616087.204</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.756</t>
+          <t>3232465.71844399</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2798945.09711714</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.477</t>
+          <t>2500708.61187664</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2781694.96200629</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.562</t>
+          <t>2989885.13847086</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.415</t>
+          <t>2944712.58670018</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.445</t>
+          <t>3039494.58227079</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3237995.53754447</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.218</t>
+          <t>3883778.96389326</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.699</t>
+          <t>3544954.20287837</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3.873</t>
+          <t>3275290.13788184</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.126</t>
+          <t>2863991.87407899</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4.729</t>
+          <t>2344233.31681373</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>5.238</t>
+          <t>1890535.11781221</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.763</t>
+          <t>1728684.53535351</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>3210527.5796199</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>2892731.00391204</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>2717054.08259785</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.314</t>
+          <t>3086578.4345196</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3286631.76758565</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.192</t>
+          <t>3378310.20950523</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>3609603.25627426</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>3802278.12261103</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.623</t>
+          <t>4469997.02311557</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>4277801.15080077</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.926</t>
+          <t>3956931.42720791</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.027</t>
+          <t>3561191.70379064</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.328</t>
+          <t>2999611.7750706</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.575</t>
+          <t>2482205.67398228</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.401</t>
+          <t>2340453.06540653</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>213.89</t>
+          <t>334641.952358483</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>205.14</t>
+          <t>339102.429593058</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>210.66</t>
+          <t>338361.947319309</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>210.81</t>
+          <t>356010.326054089</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>223.34</t>
+          <t>351545.148073966</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>218.61</t>
+          <t>349817.317809759</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>211.2</t>
+          <t>348539.985685791</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>221.71</t>
+          <t>366869.085207075</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>259.68</t>
+          <t>427267.374881465</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>229.78</t>
+          <t>492932.356022327</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>238.07</t>
+          <t>517609.757116401</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>235.5</t>
+          <t>559843.131018762</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>226.01</t>
+          <t>636358.964634236</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>219.87</t>
+          <t>704818.857878209</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>564578.924978241</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>392.91</t>
+          <t>10239804202357.6</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>379.79</t>
+          <t>9570103776774.69</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>361.54</t>
+          <t>9657611802016.23</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>364.28</t>
+          <t>11144678737954.7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>379.17</t>
+          <t>11916678495520.1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>374.26</t>
+          <t>13231072765697.8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>363.11</t>
+          <t>14022237432078.9</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>367.43</t>
+          <t>14362981262706</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>396.4</t>
+          <t>15963410917186.4</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>360.27</t>
+          <t>15270365578094.1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>362.19</t>
+          <t>14208241346811.1</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>351.31</t>
+          <t>13136520544542.5</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>344.11</t>
+          <t>11095406120815.8</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>335.03</t>
+          <t>8842239467693.96</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>329.21</t>
+          <t>6818671735234.8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>456.43</t>
+          <t>302123.13999991</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>448.17</t>
+          <t>302975.841954017</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>425.39</t>
+          <t>287321.781771823</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>420.06</t>
+          <t>308308.410831377</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>440.51</t>
+          <t>312844.666091991</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>429.8</t>
+          <t>329007.361220354</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>417.79</t>
+          <t>326535.268935928</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>417.32</t>
+          <t>338917.454608216</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>341.77</t>
+          <t>402447.844448814</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>410.71</t>
+          <t>476344.714126205</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>411.02</t>
+          <t>517951.353992813</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>398.76</t>
+          <t>569438.353670302</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>396.35</t>
+          <t>660250.998735164</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>382.2</t>
+          <t>745498.918639478</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>374.65</t>
+          <t>595525.523941251</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>72860033.945</t>
+          <t>9787699436133.3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>65895544.45</t>
+          <t>8797700433271.95</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>62164567.177</t>
+          <t>8591259432254.31</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>71692574.614</t>
+          <t>10341529538565.9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>77881669.681</t>
+          <t>11379904737270.2</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>82200706.187</t>
+          <t>13452121044243.7</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>89390019.84</t>
+          <t>14249392972489.8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>94748208.082</t>
+          <t>14338084736991</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>111527319.726</t>
+          <t>16035679325357.4</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>106846639.344</t>
+          <t>15628612114309.9</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>99379519.874</t>
+          <t>15199599033004.6</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>90319300.111</t>
+          <t>14185542093032.3</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>77178211.206</t>
+          <t>12078942570590.1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>64400535.336</t>
+          <t>10097466733274.5</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>59733656.311</t>
+          <t>7896881897321.98</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>65501715.579</t>
+          <t>32518.8123585726</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>57152499.622</t>
+          <t>36126.5876390414</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>51450329.193</t>
+          <t>51040.1655474852</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>58325467.285</t>
+          <t>47701.9152227113</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>64149181.6</t>
+          <t>38700.4819819742</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>65084626.534</t>
+          <t>20809.956589405</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>68570693.827</t>
+          <t>22004.7167498631</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>73582800.992</t>
+          <t>27951.6305988591</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>88391702.195</t>
+          <t>24819.5304326515</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>80712935.273</t>
+          <t>16587.6418961222</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>74921606.846</t>
+          <t>-341.596876412301</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>66149047.517</t>
+          <t>-9595.22265153983</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>54958205.879</t>
+          <t>-23892.0341009281</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>44579007.132</t>
+          <t>-40680.0607612691</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>40182232.353</t>
+          <t>-30946.5989630097</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>57304285.036</t>
+          <t>452104766224.274</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>51313112.643</t>
+          <t>772403343502.739</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>47689601.055</t>
+          <t>1066352369761.92</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>53934098.922</t>
+          <t>803149199388.751</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>58923652.557</t>
+          <t>536773758249.895</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>62507892.615</t>
+          <t>-221048278545.92</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>66997050.651</t>
+          <t>-227155540410.895</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>69304364.647</t>
+          <t>24896525715.059</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>79962110.333</t>
+          <t>-72268408171.0089</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>76102096.339</t>
+          <t>-358246536215.869</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>71094670.784</t>
+          <t>-991357686193.516</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>64271929.716</t>
+          <t>-1049021548489.8</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>54919695.189</t>
+          <t>-983536449774.349</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>43012919.555</t>
+          <t>-1255227265580.57</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>39043579.174</t>
+          <t>-1078210162087.17</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2.576</t>
+          <t>611707.97021</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.591</t>
+          <t>602083.05757</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2.358</t>
+          <t>541075.1991</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>557301.82177</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.464</t>
+          <t>548213.37883</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.305</t>
+          <t>493853.54953</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.336</t>
+          <t>495516.68763</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2.526</t>
+          <t>536888.96766</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3.063</t>
+          <t>651243.12978</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3.503</t>
+          <t>739343.0277</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>3.664</t>
+          <t>762241.7374</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>3.842</t>
+          <t>792088.88628</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>4.378</t>
+          <t>913676.90683</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>4.568</t>
+          <t>1003335.30351</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>4.317</t>
+          <t>913841.85861</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>35422536.501</t>
+          <t>0.0214874980478178</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>31844150.98</t>
+          <t>0.0203946882629584</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29796725.669</t>
+          <t>0.0226994586132939</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>33782470.284</t>
+          <t>0.0257024505447698</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>36357732.433</t>
+          <t>0.0248958017612591</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>37810266.865</t>
+          <t>0.0269904100510636</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>40804153.177</t>
+          <t>0.0275674707148418</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>43196279.479</t>
+          <t>0.0278214639716462</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>50705705.173</t>
+          <t>0.0292535607529896</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>48298621.874</t>
+          <t>0.0292217635208822</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>44681274.968</t>
+          <t>0.0285103754112603</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>40278256.264</t>
+          <t>0.0272658790125107</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>34487065.806</t>
+          <t>0.0288570212072069</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>28718325</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>26441556.286</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.592</t>
+          <t>814431.400719446</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>816271.905844365</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>734763.548543567</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.516</t>
+          <t>754329.977991125</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>755497.618081448</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>690557.264864149</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>699934.70624591</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>769508.450167643</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.942</t>
+          <t>947369.787305278</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.224</t>
+          <t>1078060.71345106</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2.303</t>
+          <t>1117592.42423547</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2.408</t>
+          <t>1176401.75190837</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2.749</t>
+          <t>1335242.48594087</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1485590.23912755</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.924</t>
+          <t>1407887.81680612</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>14612837.108</t>
+          <t>894246.998996653</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>13140067.769</t>
+          <t>892705.01409536</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12142305.587</t>
+          <t>801013.038454619</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>13839342.053</t>
+          <t>819008.805657723</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14756674.89</t>
+          <t>818120.744067147</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>15271069.086</t>
+          <t>745992.56218311</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16534057.979</t>
+          <t>754751.47190718</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>17494173.238</t>
+          <t>829814.613127679</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>20441878.365</t>
+          <t>1022196.98339448</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>19223220.762</t>
+          <t>1164259.26328522</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>17723808.792</t>
+          <t>1208123.46570889</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>15968154.268</t>
+          <t>1272830.95291963</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>13568254.95</t>
+          <t>1444932.84207016</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>11286524.68</t>
+          <t>1607162.91533441</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>10392051.204</t>
+          <t>1522197.41274275</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>6606237.27834427</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>6597440.64278686</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>5931238.33417218</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>5983081.67530815</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>5842802.91696989</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>5252449.91704269</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>5273150.96433174</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>5790693.10374269</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>7146351.84054792</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>8307578.21901045</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>8753350.30678464</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>9475332.64547453</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>10892653.4373844</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>880.164</t>
+          <t>894246.998996653</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>808.658</t>
+          <t>905746.400376988</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>831.834</t>
+          <t>918801.832632203</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>908.218</t>
+          <t>940052.459437422</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>980.459</t>
+          <t>981622.468584074</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1108.564</t>
+          <t>1013261.46903243</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1175.114</t>
+          <t>1032226.7139286</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1136.702</t>
+          <t>1057654.65005924</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1084.608</t>
+          <t>1073070.14098764</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>900.474</t>
+          <t>1103202.71840136</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>805.627</t>
+          <t>1126888.96813901</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>684.117</t>
+          <t>1160360.1641389</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>506.771</t>
+          <t>1187878.1231997</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>358.759</t>
+          <t>1209573.11132662</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>353.935</t>
+          <t>1198736.03069254</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>814431.400719446</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>827146.0153162</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>841812.729803576</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>864968.55688532</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>904793.59331058</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>936405.287981728</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>956795.543496221</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>979715.68502854</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>995397.987320742</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1020658.53804146</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1041840.65866083</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1071716.33593557</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1098999.10791019</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1118875.74505498</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1105441.67426647</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>510888.006383347</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>509317.22853464</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>470416.151375381</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>495170.775882277</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>482137.064452853</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>446137.70415689</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>449524.26846282</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>487014.667522321</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>600862.299735516</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>689437.746454777</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>717442.222231105</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>754135.567870367</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>882765.418839838</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>967531.233165592</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>879299.371237249</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>65501715578833.5</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>57152499621564.1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>51450329193333.6</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>58325467285363.1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>64149181599947.6</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>65084626533764.7</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>68570693826570.8</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>73582800991590.6</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>88391702195039.4</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>80712935272816</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>74921606846019.6</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>66149047517227.7</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>54958205879381</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>44579007131523.7</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>40182232352505</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>72860033944651.9</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>65895544449815</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>62164567177389.3</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>71692574614273.7</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>77881669680593.4</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>82200706186660.4</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>89390019840003.9</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>94748208081719.7</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>111527319726138</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>106846639343551</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>99379519873754.8</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>90319300110708.6</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>77178211205501.4</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>64400535335501</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>59733656310939.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>35422536500829.8</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>31844150979972</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>29796725668753.1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>33782470284402.9</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>36357732433183.3</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>37810266864668.5</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>40804153177050.6</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>43196279479382.6</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>50705705173315.8</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>48298621874445.7</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>44681274967859.4</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>40278256264128.1</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>34487065805858.2</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>28718324999600.3</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>26441556285902.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>22694100</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>22779700</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>22879400</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>23227200</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>23696500</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>24331900</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>24764500</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>24918800</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>24950200</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>24977000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>25115300</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>25362100</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>25729400</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>25944882.8155248</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>25522261.9901433</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>20263700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>20419300</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>20574300</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>20967600</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>21455400</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>22102200</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>22559900</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>22724800</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>22759200</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>22768400</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>22874800</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>23096800</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>23444000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>23580100</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>23244398.5763359</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>35398486633.4996</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>35593522062.4628</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>35567119821.5873</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>35886025437.3558</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>36560307098.763</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>36624673723.8078</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>37045328742.0656</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>36392364963.501</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>36304467884.9718</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>36998920660.15</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>37190256522.7356</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>37129413142.017</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>38094742835.7833</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>38629060336.6229</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>37490919447.5879</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>31468572871.479</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>31797297552.2686</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>31910139313.0704</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>32356772876.0978</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>33060696770.3918</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>33182201967.4061</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>33644775867.4926</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>33067659896.5064</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>33001137358.75</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>33623177266.6708</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>33760724650.5758</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>33683489572.0406</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>34563815576.0508</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>34927704665.6024</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>34397205461.9189</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.273592376994599</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.288068054217246</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.284083159498723</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.29461248402429</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.301886888327069</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.311240681765325</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.315466126812984</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.314644803851782</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.284851592450394</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.315755940723873</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.32678508147576</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.336017316639415</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.345621407234593</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.353555129748233</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.374934894575985</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.413160058376902</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.408308998377964</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.416854454368195</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.417823808883355</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.422771084810526</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.423025368000451</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.42603043269786</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.434453621079153</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.420193041419233</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.442463877183327</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.440757438924035</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.434024045809127</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.438329512209324</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.439977971085183</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.423741093157066</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.313247564628499</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.30362294740479</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.299062386133083</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.287563707092355</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.275342026862405</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.265733950234225</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.258503440489157</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.250901575069065</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.294955366130374</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.2417801820928</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.232457479600205</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.229958637551458</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.216049080556083</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.206466899166584</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.20132401226695</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.178882226288668</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.185597921936273</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.192858300507947</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.199570790221848</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.208919542052195</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.213566804948409</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.219675442988159</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.223994541614104</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.226462628785401</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.233923943837903</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.246721743340155</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.257805244546523</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.263564455118843</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.271010633571281</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.288307021141222</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.438506846401866</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.439352238166532</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.445126085625454</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.452537504695825</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.45598823932306</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.461772800360354</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.466141360726737</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.473597165484781</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.479294656517124</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.477443039611786</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.476079743991847</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.468049827173135</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.475049352150546</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.478969206372087</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.466181484681819</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.382610927309466</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.375049839897196</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.362015613866599</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.347891705082328</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.335092218624744</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.324660394691237</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.314183196285104</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.302408292901115</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.294242714697475</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.288633016550311</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.277198512667998</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.274144928280342</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.261386192730611</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.250020160056632</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.245511494176959</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2756128.53911</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2730003.4097</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2476918.08085</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2560238.46343</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2562027.48929</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2414855.70244</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2444529.532</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2639684.87457</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>3217567.05325</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>3699465.40247</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>3873089.74045</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>4125988.15742</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>4729165.05439</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>5238127.73635</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4763177.36481</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1405135.00538</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1402022.24263</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1271429.18983</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1314179.58154</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1300257.80852</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1192130.26634</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1204275.74037</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1316829.28065</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1623059.28313</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1853697.00974</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1925565.68794</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026966.52079</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2327698.26091</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2574694.1485</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2401496.78398</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>5022608.58954871</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>5086111.62977844</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>5146899.00500912</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>5219839.20163923</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>5307549.10278604</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>5406133.78864236</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5504472.44716318</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>5588962.34068851</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>5675679.49993622</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5765538.23372411</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>5861141.60089492</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5961456.63870653</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>6072128.97709865</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
